--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
   </si>
   <si>
     <t>Abstract</t>

--- a/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization-manufactureddate.xlsx
+++ b/jpcore-r4/develop-kohetest/StructureDefinition-jp-immunization-manufactureddate.xlsx
@@ -114,7 +114,7 @@
     <t>Base Definition</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/StructureDefinition/Extension|4.0.1</t>
+    <t>http://hl7.org/fhir/StructureDefinition/Extension</t>
   </si>
   <si>
     <t>Abstract</t>
